--- a/output/pdf_financials_xlsx/VITA.xlsx
+++ b/output/pdf_financials_xlsx/VITA.xlsx
@@ -3194,19 +3194,19 @@
         <v>0.100491</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.151221</v>
+        <v>4.665264</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1.955989</v>
+        <v>9.893011</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>2.002109</v>
+        <v>11.490035</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>11.459214</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>11.74539</v>
       </c>
     </row>
     <row r="93">
@@ -5078,7 +5078,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -7841,7 +7845,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -9203,7 +9211,11 @@
           <t>Warrants Reserve 17</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -10620,7 +10632,11 @@
           <t>Warrants reserve 18</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VITA.xlsx
+++ b/output/pdf_financials_xlsx/VITA.xlsx
@@ -1524,19 +1524,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.132135</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.267631</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.397337</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.715796</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.576007</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.543068</v>
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.132135</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.267631</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.397337</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.715796</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.576007</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.543068</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.683789</v>
+        <v>0.286452</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.580805</v>
+        <v>0.865009</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>18.569189</v>
+        <v>17.993182</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>6.471302</v>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
@@ -25974,7 +25974,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">

--- a/output/pdf_financials_xlsx/VITA.xlsx
+++ b/output/pdf_financials_xlsx/VITA.xlsx
@@ -1186,10 +1186,8 @@
       <c r="G23" s="3" t="n">
         <v>4.171904</v>
       </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H23" s="3" t="n">
+        <v>-3.582443</v>
       </c>
     </row>
     <row r="24">
@@ -2399,13 +2397,13 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>1.781439</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>3.56578</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>1.040881</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0</v>
@@ -2480,16 +2478,16 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.715763</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.840006</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>6.539012</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.793004</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0</v>
@@ -3382,10 +3380,8 @@
       <c r="G99" s="3" t="n">
         <v>4.171904</v>
       </c>
-      <c r="H99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H99" s="3" t="n">
+        <v>-3.582443</v>
       </c>
     </row>
     <row r="100">
@@ -3681,13 +3677,13 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>2.57152</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.315191</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.241211</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -12835,7 +12831,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -14386,7 +14386,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -15204,7 +15208,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -16895,7 +16903,11 @@
           <t>Accretion 16</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -17297,7 +17309,11 @@
           <t>Deferred tax (recovery)</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -22491,7 +22507,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -24403,7 +24423,11 @@
           <t>Income tax recovery 20</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
